--- a/rules_ideal_acceptable_csv.xlsx
+++ b/rules_ideal_acceptable_csv.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="130">
   <si>
     <t>feature_type</t>
   </si>
@@ -251,9 +251,6 @@
     <t>Battery, Petrol</t>
   </si>
   <si>
-    <t>2/3/4-tooth blade, circular blade, Nylon line</t>
-  </si>
-  <si>
     <t>Petrol, Electric</t>
   </si>
   <si>
@@ -381,15 +378,6 @@
   </si>
   <si>
     <t>3–6 kg, 9–13 kg</t>
-  </si>
-  <si>
-    <t>plastic blade, Nylon line</t>
-  </si>
-  <si>
-    <t>plastic blade, Nylon line, 2/3/4-tooth blade</t>
-  </si>
-  <si>
-    <t>2/3/4-tooth blade, circular blade</t>
   </si>
   <si>
     <t>D-loop, D-loop</t>
@@ -1290,7 +1278,10 @@
   <cols>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="50.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" customWidth="1"/>
+    <col min="7" max="7" width="29.42578125" customWidth="1"/>
+    <col min="12" max="12" width="34.85546875" customWidth="1"/>
+    <col min="13" max="13" width="42" customWidth="1"/>
     <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="21" max="21" width="23.85546875" customWidth="1"/>
     <col min="22" max="22" width="26" customWidth="1"/>
@@ -1388,7 +1379,7 @@
         <v>63</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF1" s="2" t="s">
         <v>64</v>
@@ -1405,7 +1396,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1">
         <v>5.3</v>
@@ -1414,7 +1405,7 @@
         <v>65</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" s="1">
         <v>6.9</v>
@@ -1423,7 +1414,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K2" s="1">
         <v>5.7</v>
@@ -1432,7 +1423,7 @@
         <v>54</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N2" s="1">
         <v>9.6</v>
@@ -1450,16 +1441,16 @@
         <v>36</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T2" s="1">
         <v>6.1</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="W2" s="1">
         <v>9.1999999999999993</v>
@@ -1468,7 +1459,7 @@
         <v>37</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z2" s="1">
         <v>7.3</v>
@@ -1477,7 +1468,7 @@
         <v>38</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC2" s="1">
         <v>8.4</v>
@@ -1503,13 +1494,13 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E3" s="1">
         <v>5.3</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>69</v>
@@ -1521,7 +1512,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K3" s="1">
         <v>5.7</v>
@@ -1530,7 +1521,7 @@
         <v>34</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N3" s="1">
         <v>9.6</v>
@@ -1548,7 +1539,7 @@
         <v>42</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T3" s="1">
         <v>6.1</v>
@@ -1566,7 +1557,7 @@
         <v>44</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Z3" s="1">
         <v>7.3</v>
@@ -1575,7 +1566,7 @@
         <v>45</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AC3" s="1">
         <v>8.4</v>
@@ -1601,7 +1592,7 @@
         <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4" s="1">
         <v>5.3</v>
@@ -1610,7 +1601,7 @@
         <v>65</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="1">
         <v>6.9</v>
@@ -1619,16 +1610,16 @@
         <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K4" s="1">
         <v>5.7</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="N4" s="1">
         <v>9.6</v>
@@ -1643,10 +1634,10 @@
         <v>8</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="T4" s="1">
         <v>6.1</v>
@@ -1664,7 +1655,7 @@
         <v>49</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z4" s="1">
         <v>7.3</v>
@@ -1673,7 +1664,7 @@
         <v>50</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AC4" s="1">
         <v>8.4</v>
@@ -1699,16 +1690,16 @@
         <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" s="1">
         <v>2.8</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="H5" s="1">
         <v>4.4000000000000004</v>
@@ -1717,16 +1708,16 @@
         <v>41</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K5" s="1">
         <v>3.2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N5" s="1">
         <v>7.1</v>
@@ -1741,10 +1732,10 @@
         <v>5.5</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T5" s="1">
         <v>3.6</v>
@@ -1759,19 +1750,19 @@
         <v>6.7</v>
       </c>
       <c r="X5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="Z5" s="1">
         <v>4.8</v>
       </c>
       <c r="AA5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB5" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="AC5" s="1">
         <v>5.9</v>
@@ -1797,16 +1788,16 @@
         <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1">
         <v>2.8</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="H6" s="1">
         <v>4.4000000000000004</v>
@@ -1824,7 +1815,7 @@
         <v>54</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N6" s="1">
         <v>7.1</v>
@@ -1839,10 +1830,10 @@
         <v>5.5</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T6" s="1">
         <v>3.6</v>
@@ -1860,7 +1851,7 @@
         <v>37</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Z6" s="1">
         <v>4.8</v>
@@ -1869,7 +1860,7 @@
         <v>38</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC6" s="1">
         <v>5.9</v>
@@ -1895,13 +1886,13 @@
         <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" s="1">
         <v>2.8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>71</v>
@@ -1913,7 +1904,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K7" s="1">
         <v>3.2</v>
@@ -1922,7 +1913,7 @@
         <v>34</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N7" s="1">
         <v>7.1</v>
@@ -1940,7 +1931,7 @@
         <v>36</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="T7" s="1">
         <v>3.6</v>
@@ -1958,7 +1949,7 @@
         <v>37</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Z7" s="1">
         <v>4.8</v>
@@ -1967,7 +1958,7 @@
         <v>38</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AC7" s="1">
         <v>5.9</v>
@@ -1993,16 +1984,16 @@
         <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1">
         <v>1.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H8" s="1">
         <v>3.1</v>
@@ -2011,7 +2002,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K8" s="1">
         <v>1.9</v>
@@ -2020,7 +2011,7 @@
         <v>54</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N8" s="1">
         <v>5.8</v>
@@ -2038,7 +2029,7 @@
         <v>36</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T8" s="1">
         <v>2.2999999999999998</v>
@@ -2056,7 +2047,7 @@
         <v>37</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z8" s="1">
         <v>3.5</v>
@@ -2065,7 +2056,7 @@
         <v>38</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC8" s="1">
         <v>4.5999999999999996</v>
@@ -2091,16 +2082,16 @@
         <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="1">
         <v>1.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H9" s="1">
         <v>3.1</v>
@@ -2109,16 +2100,16 @@
         <v>33</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K9" s="1">
         <v>1.9</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N9" s="1">
         <v>5.8</v>
@@ -2127,16 +2118,16 @@
         <v>35</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="1">
         <v>4.2</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T9" s="1">
         <v>2.2999999999999998</v>
@@ -2154,22 +2145,22 @@
         <v>37</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="Z9" s="1">
         <v>3.5</v>
       </c>
       <c r="AA9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB9" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="AC9" s="1">
         <v>4.5999999999999996</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1">
@@ -2184,19 +2175,19 @@
         <v>60</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="H10" s="1">
         <v>5.6</v>
@@ -2214,7 +2205,7 @@
         <v>54</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N10" s="1">
         <v>8.3000000000000007</v>
@@ -2232,7 +2223,7 @@
         <v>36</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="T10" s="1">
         <v>4.8</v>
@@ -2247,10 +2238,10 @@
         <v>7.9</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Z10" s="1">
         <v>6</v>
@@ -2259,7 +2250,7 @@
         <v>38</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC10" s="1">
         <v>7.1</v>
@@ -2285,7 +2276,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
@@ -2294,7 +2285,7 @@
         <v>32</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" s="1">
         <v>5.6</v>
@@ -2303,7 +2294,7 @@
         <v>41</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K11" s="1">
         <v>4.4000000000000004</v>
@@ -2312,7 +2303,7 @@
         <v>48</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N11" s="1">
         <v>8.3000000000000007</v>
@@ -2330,7 +2321,7 @@
         <v>42</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="T11" s="1">
         <v>4.8</v>
@@ -2348,7 +2339,7 @@
         <v>44</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="Z11" s="1">
         <v>6</v>
@@ -2357,13 +2348,13 @@
         <v>45</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AC11" s="1">
         <v>7.1</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1">
@@ -2378,10 +2369,10 @@
         <v>62</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
@@ -2390,7 +2381,7 @@
         <v>47</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H12" s="1">
         <v>5.6</v>
@@ -2399,7 +2390,7 @@
         <v>41</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K12" s="1">
         <v>4.4000000000000004</v>
@@ -2408,7 +2399,7 @@
         <v>48</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="N12" s="1">
         <v>8.3000000000000007</v>
@@ -2423,10 +2414,10 @@
         <v>6.7</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="T12" s="1">
         <v>4.8</v>
@@ -2444,7 +2435,7 @@
         <v>49</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z12" s="1">
         <v>6</v>
@@ -2453,7 +2444,7 @@
         <v>50</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AC12" s="1">
         <v>7.1</v>
